--- a/data/trans_dic/P22$concerEmp-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,77</t>
+          <t>1,69; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,37 +732,37 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,57</t>
+          <t>0,89; 2,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,53</t>
+          <t>1,84; 4,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,72</t>
+          <t>0,7; 2,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,47</t>
+          <t>0,28; 2,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,45</t>
+          <t>0,65; 4,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,35</t>
+          <t>0,57; 2,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,99</t>
+          <t>0,36; 2,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,66</t>
+          <t>0,17; 1,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,04</t>
+          <t>1,42; 3,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,94</t>
+          <t>0,74; 1,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,5</t>
+          <t>0,28; 1,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,37</t>
+          <t>0,57; 2,58</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,84</t>
+          <t>2,17; 4,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,86</t>
+          <t>0,96; 2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,02</t>
+          <t>0,3; 1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,05</t>
+          <t>1,33; 4,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,95</t>
+          <t>0,34; 1,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,18</t>
+          <t>0,14; 1,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,44</t>
+          <t>0,26; 1,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,07</t>
+          <t>1,38; 2,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,76</t>
+          <t>0,62; 1,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,4</t>
+          <t>0,41; 1,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,52</t>
+          <t>0,88; 2,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,57</t>
+          <t>0,99; 3,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,95</t>
+          <t>0,83; 3,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,64</t>
+          <t>0,15; 1,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,71</t>
+          <t>0,46; 2,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,71</t>
+          <t>0,16; 1,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,26</t>
+          <t>0,15; 1,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,13</t>
+          <t>0,69; 2,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,25</t>
+          <t>0,69; 2,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,09</t>
+          <t>0,53; 2,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,11</t>
+          <t>0,19; 1,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,03</t>
+          <t>0,75; 2,11</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,78</t>
+          <t>0,44; 2,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,19</t>
+          <t>0,23; 1,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,32</t>
+          <t>1,14; 3,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,61</t>
+          <t>0,36; 1,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,4</t>
+          <t>0,24; 1,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,23</t>
+          <t>0,13; 1,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,27</t>
+          <t>0,87; 2,22</t>
         </is>
       </c>
     </row>
@@ -1417,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,83</t>
+          <t>0,06; 0,93</t>
         </is>
       </c>
     </row>
@@ -1697,52 +1697,52 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,8</t>
+          <t>1,77; 2,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,57</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,92</t>
+          <t>0,31; 0,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,93</t>
+          <t>0,93; 1,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,86</t>
+          <t>0,34; 0,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,62</t>
+          <t>0,22; 0,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,59</t>
+          <t>0,2; 0,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,91</t>
+          <t>0,43; 0,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,68</t>
+          <t>1,11; 1,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,02</t>
+          <t>0,56; 0,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,29</t>
+          <t>0,78; 1,3</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7714; 23527</t>
+          <t>8315; 24212</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 5308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9530</t>
+          <t>0; 9518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 13734</t>
+          <t>0; 12518</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4833</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5192</t>
+          <t>0; 4968</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6703</t>
+          <t>0; 5178</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8588</t>
+          <t>0; 8767</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8581; 24686</t>
+          <t>8550; 26323</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 8008</t>
+          <t>0; 7003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1029; 10251</t>
+          <t>1029; 10277</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 14461</t>
+          <t>0; 13453</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13972; 33181</t>
+          <t>13507; 32320</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5561; 18674</t>
+          <t>4831; 17407</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1661; 14613</t>
+          <t>1672; 15959</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2827; 18842</t>
+          <t>2734; 17620</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3521; 14703</t>
+          <t>3549; 15529</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2360; 12117</t>
+          <t>2190; 12705</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6193</t>
+          <t>0; 6086</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>841; 8481</t>
+          <t>858; 9911</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19944; 41343</t>
+          <t>19244; 41275</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8756; 25177</t>
+          <t>9542; 25447</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3323; 17298</t>
+          <t>3182; 16686</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5230; 22135</t>
+          <t>5336; 24086</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13873; 30918</t>
+          <t>13846; 31795</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6552; 19507</t>
+          <t>6538; 19659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1932; 13492</t>
+          <t>2015; 13284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6779; 21727</t>
+          <t>7139; 22692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2207; 13426</t>
+          <t>2327; 13645</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>964; 8420</t>
+          <t>962; 7344</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1781; 10351</t>
+          <t>1787; 10402</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1402; 7787</t>
+          <t>1402; 7867</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19197; 40723</t>
+          <t>18358; 39461</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8666; 24550</t>
+          <t>8574; 22954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5377; 18573</t>
+          <t>5480; 19456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9548; 27229</t>
+          <t>9455; 27199</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4773; 18516</t>
+          <t>5139; 19231</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5512; 24261</t>
+          <t>5099; 23007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>991; 10587</t>
+          <t>986; 10444</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4037; 24097</t>
+          <t>4108; 23830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>801; 8795</t>
+          <t>802; 8579</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6879</t>
+          <t>0; 6208</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>990; 8157</t>
+          <t>997; 9237</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4849; 15156</t>
+          <t>4936; 15277</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7684; 23184</t>
+          <t>7108; 22489</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6429; 25714</t>
+          <t>6527; 27113</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2477; 14342</t>
+          <t>2522; 13601</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11455; 32544</t>
+          <t>11970; 33728</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1897; 10759</t>
+          <t>1690; 10994</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1000; 9389</t>
+          <t>1008; 8348</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5027</t>
+          <t>0; 5746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5801; 18659</t>
+          <t>6387; 19773</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4873</t>
+          <t>0; 5698</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6797</t>
+          <t>0; 7688</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1895; 8779</t>
+          <t>1937; 8420</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1885; 11042</t>
+          <t>1895; 10827</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1062; 10775</t>
+          <t>1129; 10551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>998; 8616</t>
+          <t>994; 8356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9481; 25072</t>
+          <t>9631; 24523</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5958</t>
+          <t>0; 5278</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5276</t>
+          <t>0; 5191</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 5063</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2458</t>
+          <t>0; 2453</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5902</t>
+          <t>0; 4802</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5237</t>
+          <t>0; 5364</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 5572</t>
+          <t>0; 5427</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1823</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4850</t>
+          <t>0; 4568</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4295</t>
+          <t>0; 5326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2202</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2127</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2544</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3273</t>
+          <t>0; 3566</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4746</t>
+          <t>0; 4801</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2088</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>437; 5856</t>
+          <t>437; 6623</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>58910; 91539</t>
+          <t>57796; 91154</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27146; 53641</t>
+          <t>28703; 54769</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11358; 31139</t>
+          <t>10391; 31425</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33658; 66724</t>
+          <t>32078; 65780</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11173; 28937</t>
+          <t>11325; 29491</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7093; 22154</t>
+          <t>7912; 22079</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6866; 21055</t>
+          <t>7040; 21098</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15751; 33438</t>
+          <t>15663; 33003</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>74200; 112004</t>
+          <t>73991; 113186</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38600; 70893</t>
+          <t>38861; 69011</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22121; 45723</t>
+          <t>21825; 45532</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>56288; 91591</t>
+          <t>55461; 92328</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerEmp-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,91</t>
+          <t>1,57; 4,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,74</t>
+          <t>0,95; 2,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,26</t>
+          <t>0,13; 1,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,41</t>
+          <t>1,97; 4,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,53</t>
+          <t>0,7; 2,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,7</t>
+          <t>0,28; 2,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,16</t>
+          <t>0,82; 4,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,48</t>
+          <t>0,59; 2,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,08</t>
+          <t>0,46; 2,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,94</t>
+          <t>0,18; 1,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,04</t>
+          <t>1,51; 3,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,96</t>
+          <t>0,72; 1,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,45</t>
+          <t>0,29; 1,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,58</t>
+          <t>0,65; 2,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,98</t>
+          <t>2,15; 4,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,88</t>
+          <t>0,89; 2,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,99</t>
+          <t>0,29; 2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,23</t>
+          <t>1,14; 3,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,98</t>
+          <t>0,32; 1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,03</t>
+          <t>0,14; 1,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,57</t>
+          <t>0,27; 1,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,45</t>
+          <t>0,24; 1,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,97</t>
+          <t>1,39; 2,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,65</t>
+          <t>0,63; 1,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,46</t>
+          <t>0,38; 1,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,52</t>
+          <t>0,83; 2,29</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,71</t>
+          <t>1,04; 3,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,74</t>
+          <t>0,82; 3,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,62</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,68</t>
+          <t>1,03; 3,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,67</t>
+          <t>0,16; 1,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,43</t>
+          <t>0,15; 1,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,14</t>
+          <t>0,72; 2,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,18</t>
+          <t>0,7; 2,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,2</t>
+          <t>0,5; 2,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,05</t>
+          <t>0,16; 1,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,11</t>
+          <t>1,08; 2,45</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,84</t>
+          <t>0,49; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,94</t>
+          <t>0,24; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,52</t>
+          <t>0,99; 3,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,54</t>
+          <t>0,34; 1,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,37</t>
+          <t>0,21; 1,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,2</t>
+          <t>0,12; 1,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,86</t>
+          <t>0,1; 0,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,22</t>
+          <t>0,84; 2,24</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,93</t>
+          <t>0,06; 0,85</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,79</t>
+          <t>1,76; 2,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,6</t>
+          <t>0,8; 1,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,93</t>
+          <t>0,32; 0,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,9</t>
+          <t>1,08; 2,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,87</t>
+          <t>0,32; 0,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,62</t>
+          <t>0,19; 0,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,6</t>
+          <t>0,19; 0,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,9</t>
+          <t>0,47; 0,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,7</t>
+          <t>1,1; 1,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,99</t>
+          <t>0,55; 0,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,66</t>
+          <t>0,32; 0,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,3</t>
+          <t>0,81; 1,32</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4318</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8315; 24212</t>
+          <t>7747; 24396</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5308</t>
+          <t>0; 5272</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9518</t>
+          <t>0; 9354</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 12518</t>
+          <t>0; 13767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 5039</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4968</t>
+          <t>0; 4911</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5178</t>
+          <t>0; 5123</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8767</t>
+          <t>0; 8753</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8550; 26323</t>
+          <t>9079; 25601</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7003</t>
+          <t>0; 6231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1029; 10277</t>
+          <t>1022; 10147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 13453</t>
+          <t>0; 15055</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>13009</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13507; 32320</t>
+          <t>14414; 34219</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4831; 17407</t>
+          <t>4779; 17542</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1672; 15959</t>
+          <t>1664; 14899</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2734; 17620</t>
+          <t>3912; 21859</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3549; 15529</t>
+          <t>3705; 15303</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2190; 12705</t>
+          <t>2796; 12834</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6086</t>
+          <t>0; 5607</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>858; 9911</t>
+          <t>881; 9028</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19244; 41275</t>
+          <t>20558; 42323</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9542; 25447</t>
+          <t>9280; 25450</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3182; 16686</t>
+          <t>3316; 17288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5336; 24086</t>
+          <t>6302; 23973</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16672</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13846; 31795</t>
+          <t>13707; 31666</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6538; 19659</t>
+          <t>6078; 19996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2015; 13284</t>
+          <t>1915; 13614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7139; 22692</t>
+          <t>7068; 21606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2327; 13645</t>
+          <t>2195; 13159</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>962; 7344</t>
+          <t>974; 8717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1787; 10402</t>
+          <t>1770; 10480</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1402; 7867</t>
+          <t>1471; 8645</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18358; 39461</t>
+          <t>18474; 38550</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8574; 22954</t>
+          <t>8801; 23737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5480; 19456</t>
+          <t>5001; 19750</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9455; 27199</t>
+          <t>10353; 28518</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>23013</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5139; 19231</t>
+          <t>5398; 18915</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5099; 23007</t>
+          <t>5068; 23643</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>986; 10444</t>
+          <t>993; 9303</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4108; 23830</t>
+          <t>7188; 24252</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>802; 8579</t>
+          <t>802; 8617</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6208</t>
+          <t>0; 6207</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>997; 9237</t>
+          <t>993; 8368</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4936; 15277</t>
+          <t>5294; 15757</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7108; 22489</t>
+          <t>7203; 22225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6527; 27113</t>
+          <t>6205; 24661</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2522; 13601</t>
+          <t>2129; 13256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11970; 33728</t>
+          <t>15562; 35244</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15731</t>
+          <t>16970</t>
         </is>
       </c>
     </row>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1690; 10994</t>
+          <t>1882; 10415</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1008; 8348</t>
+          <t>1010; 8602</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5746</t>
+          <t>0; 5693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6387; 19773</t>
+          <t>6059; 21393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2925,37 +2925,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5698</t>
+          <t>0; 5278</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7688</t>
+          <t>0; 7657</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1937; 8420</t>
+          <t>2065; 9698</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1895; 10827</t>
+          <t>1697; 11111</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1129; 10551</t>
+          <t>1052; 9923</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>994; 8356</t>
+          <t>994; 8542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9631; 24523</t>
+          <t>10216; 27325</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1324</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 5950</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5191</t>
+          <t>0; 5201</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5063</t>
+          <t>0; 4496</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2453</t>
+          <t>0; 2165</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4802</t>
+          <t>0; 5263</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5364</t>
+          <t>0; 5207</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 5427</t>
+          <t>0; 4769</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2117</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 4439</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5326</t>
+          <t>0; 5454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3566</t>
+          <t>0; 4056</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>437; 6623</t>
+          <t>453; 6564</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>52667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>77422</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>57796; 91154</t>
+          <t>57515; 93141</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28703; 54769</t>
+          <t>27511; 55618</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10391; 31425</t>
+          <t>10884; 32188</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32078; 65780</t>
+          <t>38292; 72093</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11325; 29491</t>
+          <t>10797; 28701</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7912; 22079</t>
+          <t>6884; 21084</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7040; 21098</t>
+          <t>6799; 20757</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15663; 33003</t>
+          <t>17557; 35815</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>73991; 113186</t>
+          <t>73090; 113063</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38861; 69011</t>
+          <t>38721; 69164</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21825; 45532</t>
+          <t>22216; 48325</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>55461; 92328</t>
+          <t>58899; 95990</t>
         </is>
       </c>
     </row>
